--- a/docs/Database.xlsx
+++ b/docs/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\procedure\rdc2-portal\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D899BE4-7F6D-4681-BD97-3D8103B2DD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A3419A-9A43-4483-8F87-81586F43226E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
